--- a/source_data/Extended_Data_Fig_3_source_data.xlsx
+++ b/source_data/Extended_Data_Fig_3_source_data.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cluster-count diagnostics</t>
+          <t>Clustering of GCIRI and capacity strengths</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Standardized GCIRI and three capacity strengths are clustered for four to eight clusters. Silhouette summarizes internal separation, and adjusted Rand index (ARI) and normalized mutual information (NMI) compare the clustering with the six rule-defined patterns. These are separate questions: cluster quality does not establish that the six patterns are natural clusters.</t>
+          <t>Standardized GCIRI and three capacity strengths are clustered for four to eight clusters. Silhouette summarizes internal separation, and adjusted Rand index (ARI) and normalized mutual information (NMI) compare the clustering with the six rule-defined patterns.</t>
         </is>
       </c>
     </row>
@@ -531,13 +531,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3501735493334373</v>
+        <v>0.3511209949238706</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3525833615651258</v>
+        <v>0.3539523630221025</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4532339364053263</v>
+        <v>0.4531677248861482</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -548,13 +548,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3573108591136145</v>
+        <v>0.3578174815177845</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2566311705497469</v>
+        <v>0.2573169056590427</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4079002841776014</v>
+        <v>0.4083635661386707</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3571349896785677</v>
+        <v>0.3574210349541116</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2874420030027936</v>
+        <v>0.2885254583221864</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4277802253153408</v>
+        <v>0.4289068199905018</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -582,13 +582,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3585771491091917</v>
+        <v>0.3588261735117027</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3201326252442536</v>
+        <v>0.3205651256204261</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4860685668511663</v>
+        <v>0.48571359232048</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -599,13 +599,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3461546468723734</v>
+        <v>0.3460690761314903</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2934529788595019</v>
+        <v>0.2969871701164212</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4648082146921919</v>
+        <v>0.4671052113469459</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
